--- a/Hoadon/HDRa/12/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDRa/12/3502550210_HDDienTuMayTinhTien.xlsx
@@ -9433,6 +9433,615 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="4" t="n">
+        <v>136.0</v>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>3129</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H142" s="7"/>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>752 trần phú</t>
+        </is>
+      </c>
+      <c r="J142" s="6" t="inlineStr">
+        <is>
+          <t>752 trần phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K142" s="6"/>
+      <c r="L142" s="13" t="n">
+        <v>6068677.0</v>
+      </c>
+      <c r="M142" s="13" t="n">
+        <v>605313.0</v>
+      </c>
+      <c r="N142" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O142" s="13" t="n">
+        <v>6673990.0</v>
+      </c>
+      <c r="P142" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q142" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="n">
+        <v>137.0</v>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H143" s="7"/>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>335/4 Trần Phú</t>
+        </is>
+      </c>
+      <c r="J143" s="6" t="inlineStr">
+        <is>
+          <t>335/4 Trần Phú , Phường Vũng Tàu Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K143" s="6"/>
+      <c r="L143" s="13" t="n">
+        <v>4939529.0</v>
+      </c>
+      <c r="M143" s="13" t="n">
+        <v>464453.0</v>
+      </c>
+      <c r="N143" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O143" s="13" t="n">
+        <v>5403982.0</v>
+      </c>
+      <c r="P143" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q143" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="n">
+        <v>138.0</v>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H144" s="7"/>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>66 Võ Trường Toản</t>
+        </is>
+      </c>
+      <c r="J144" s="6" t="inlineStr">
+        <is>
+          <t>66 Võ Trường Toản, Phường Tam Thắng, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K144" s="6"/>
+      <c r="L144" s="13" t="n">
+        <v>5915333.0</v>
+      </c>
+      <c r="M144" s="13" t="n">
+        <v>532644.0</v>
+      </c>
+      <c r="N144" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O144" s="13" t="n">
+        <v>6447977.0</v>
+      </c>
+      <c r="P144" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q144" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="n">
+        <v>139.0</v>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>3132</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H145" s="7"/>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J145" s="6"/>
+      <c r="K145" s="6"/>
+      <c r="L145" s="13" t="n">
+        <v>6051520.0</v>
+      </c>
+      <c r="M145" s="13" t="n">
+        <v>547485.0</v>
+      </c>
+      <c r="N145" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O145" s="13" t="n">
+        <v>6599005.0</v>
+      </c>
+      <c r="P145" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q145" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="n">
+        <v>140.0</v>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>3133</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H146" s="7"/>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J146" s="6"/>
+      <c r="K146" s="6"/>
+      <c r="L146" s="13" t="n">
+        <v>5537616.0</v>
+      </c>
+      <c r="M146" s="13" t="n">
+        <v>536375.0</v>
+      </c>
+      <c r="N146" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O146" s="13" t="n">
+        <v>6073991.0</v>
+      </c>
+      <c r="P146" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q146" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="n">
+        <v>141.0</v>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>3134</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="F147" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H147" s="7"/>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>348 trần phú</t>
+        </is>
+      </c>
+      <c r="J147" s="6" t="inlineStr">
+        <is>
+          <t>348 trần phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh.</t>
+        </is>
+      </c>
+      <c r="K147" s="6"/>
+      <c r="L147" s="13" t="n">
+        <v>6091069.0</v>
+      </c>
+      <c r="M147" s="13" t="n">
+        <v>550922.0</v>
+      </c>
+      <c r="N147" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O147" s="13" t="n">
+        <v>6641991.0</v>
+      </c>
+      <c r="P147" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q147" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="n">
+        <v>142.0</v>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>3135</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H148" s="7"/>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>562/19 Trần Phú</t>
+        </is>
+      </c>
+      <c r="J148" s="6" t="inlineStr">
+        <is>
+          <t>562/19 Trần Phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K148" s="6"/>
+      <c r="L148" s="13" t="n">
+        <v>6269024.0</v>
+      </c>
+      <c r="M148" s="13" t="n">
+        <v>614976.0</v>
+      </c>
+      <c r="N148" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O148" s="13" t="n">
+        <v>6884000.0</v>
+      </c>
+      <c r="P148" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q148" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="n">
+        <v>143.0</v>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>3136</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H149" s="7"/>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J149" s="6"/>
+      <c r="K149" s="6"/>
+      <c r="L149" s="13" t="n">
+        <v>5834309.0</v>
+      </c>
+      <c r="M149" s="13" t="n">
+        <v>559189.0</v>
+      </c>
+      <c r="N149" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O149" s="13" t="n">
+        <v>6393498.0</v>
+      </c>
+      <c r="P149" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q149" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="n">
+        <v>144.0</v>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>3137</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H150" s="7"/>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>366 TRẦN PHÚ</t>
+        </is>
+      </c>
+      <c r="J150" s="6" t="inlineStr">
+        <is>
+          <t>366 trần phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K150" s="6"/>
+      <c r="L150" s="13" t="n">
+        <v>7268772.0</v>
+      </c>
+      <c r="M150" s="13" t="n">
+        <v>708230.0</v>
+      </c>
+      <c r="N150" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O150" s="13" t="n">
+        <v>7977002.0</v>
+      </c>
+      <c r="P150" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q150" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>

--- a/Hoadon/HDRa/12/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDRa/12/3502550210_HDDienTuMayTinhTien.xlsx
@@ -10042,6 +10042,339 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" s="4" t="n">
+        <v>145.0</v>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>3138</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H151" s="7"/>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>ốc sốt</t>
+        </is>
+      </c>
+      <c r="J151" s="6"/>
+      <c r="K151" s="6"/>
+      <c r="L151" s="13" t="n">
+        <v>2.1593793E7</v>
+      </c>
+      <c r="M151" s="13" t="n">
+        <v>1727504.0</v>
+      </c>
+      <c r="N151" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O151" s="13" t="n">
+        <v>2.3321297E7</v>
+      </c>
+      <c r="P151" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q151" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="n">
+        <v>146.0</v>
+      </c>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>3139</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H152" s="7"/>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>135 trần phú</t>
+        </is>
+      </c>
+      <c r="J152" s="6" t="inlineStr">
+        <is>
+          <t>135 trần phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K152" s="6"/>
+      <c r="L152" s="13" t="n">
+        <v>6298276.0</v>
+      </c>
+      <c r="M152" s="13" t="n">
+        <v>514317.0</v>
+      </c>
+      <c r="N152" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O152" s="13" t="n">
+        <v>6812593.0</v>
+      </c>
+      <c r="P152" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q152" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="n">
+        <v>147.0</v>
+      </c>
+      <c r="B153" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>3140</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="F153" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H153" s="7"/>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J153" s="6"/>
+      <c r="K153" s="6"/>
+      <c r="L153" s="13" t="n">
+        <v>7538573.0</v>
+      </c>
+      <c r="M153" s="13" t="n">
+        <v>729450.0</v>
+      </c>
+      <c r="N153" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O153" s="13" t="n">
+        <v>8268023.0</v>
+      </c>
+      <c r="P153" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q153" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="n">
+        <v>148.0</v>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr">
+        <is>
+          <t>3141</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H154" s="7"/>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>36/9 nguyễn an ninh</t>
+        </is>
+      </c>
+      <c r="J154" s="6" t="inlineStr">
+        <is>
+          <t>36/9 nguyễn an ninh, Phường Tam Thắng Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K154" s="6"/>
+      <c r="L154" s="13" t="n">
+        <v>7725653.0</v>
+      </c>
+      <c r="M154" s="13" t="n">
+        <v>718342.0</v>
+      </c>
+      <c r="N154" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O154" s="13" t="n">
+        <v>8443995.0</v>
+      </c>
+      <c r="P154" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q154" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="n">
+        <v>149.0</v>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="inlineStr">
+        <is>
+          <t>3142</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>17/12/2025</t>
+        </is>
+      </c>
+      <c r="F155" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G155" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H155" s="7"/>
+      <c r="I155" s="6"/>
+      <c r="J155" s="6" t="inlineStr">
+        <is>
+          <t>59 hoàng việt,Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K155" s="6"/>
+      <c r="L155" s="13" t="n">
+        <v>7854032.0</v>
+      </c>
+      <c r="M155" s="13" t="n">
+        <v>635848.0</v>
+      </c>
+      <c r="N155" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O155" s="13" t="n">
+        <v>8489880.0</v>
+      </c>
+      <c r="P155" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q155" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>

--- a/Hoadon/HDRa/12/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDRa/12/3502550210_HDDienTuMayTinhTien.xlsx
@@ -10375,6 +10375,339 @@
         </is>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" s="4" t="n">
+        <v>150.0</v>
+      </c>
+      <c r="B156" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D156" s="7" t="inlineStr">
+        <is>
+          <t>3143</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>18/12/2025</t>
+        </is>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H156" s="7"/>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>Tiệm cơm chị hà</t>
+        </is>
+      </c>
+      <c r="J156" s="6"/>
+      <c r="K156" s="6"/>
+      <c r="L156" s="13" t="n">
+        <v>4966767.0</v>
+      </c>
+      <c r="M156" s="13" t="n">
+        <v>480287.0</v>
+      </c>
+      <c r="N156" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O156" s="13" t="n">
+        <v>5447054.0</v>
+      </c>
+      <c r="P156" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q156" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="n">
+        <v>151.0</v>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D157" s="7" t="inlineStr">
+        <is>
+          <t>3144</t>
+        </is>
+      </c>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t>18/12/2025</t>
+        </is>
+      </c>
+      <c r="F157" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H157" s="7"/>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J157" s="6"/>
+      <c r="K157" s="6"/>
+      <c r="L157" s="13" t="n">
+        <v>6187809.0</v>
+      </c>
+      <c r="M157" s="13" t="n">
+        <v>553171.0</v>
+      </c>
+      <c r="N157" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O157" s="13" t="n">
+        <v>6740980.0</v>
+      </c>
+      <c r="P157" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q157" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="n">
+        <v>152.0</v>
+      </c>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>3145</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
+          <t>18/12/2025</t>
+        </is>
+      </c>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H158" s="7"/>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>31 Viba</t>
+        </is>
+      </c>
+      <c r="J158" s="6" t="inlineStr">
+        <is>
+          <t>31 Viba , Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K158" s="6"/>
+      <c r="L158" s="13" t="n">
+        <v>4339809.0</v>
+      </c>
+      <c r="M158" s="13" t="n">
+        <v>347185.0</v>
+      </c>
+      <c r="N158" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O158" s="13" t="n">
+        <v>4686994.0</v>
+      </c>
+      <c r="P158" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q158" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="n">
+        <v>153.0</v>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>3146</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>18/12/2025</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G159" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H159" s="7"/>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>Cô Vân</t>
+        </is>
+      </c>
+      <c r="J159" s="6" t="inlineStr">
+        <is>
+          <t>790 trần phú, Phường Vũng Tàu Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K159" s="6"/>
+      <c r="L159" s="13" t="n">
+        <v>3281681.0</v>
+      </c>
+      <c r="M159" s="13" t="n">
+        <v>286172.0</v>
+      </c>
+      <c r="N159" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O159" s="13" t="n">
+        <v>3567853.0</v>
+      </c>
+      <c r="P159" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q159" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="n">
+        <v>154.0</v>
+      </c>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>3147</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>18/12/2025</t>
+        </is>
+      </c>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H160" s="7"/>
+      <c r="I160" s="6"/>
+      <c r="J160" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K160" s="6"/>
+      <c r="L160" s="13" t="n">
+        <v>8471548.0</v>
+      </c>
+      <c r="M160" s="13" t="n">
+        <v>840452.0</v>
+      </c>
+      <c r="N160" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O160" s="13" t="n">
+        <v>9312000.0</v>
+      </c>
+      <c r="P160" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q160" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>

--- a/Hoadon/HDRa/12/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDRa/12/3502550210_HDDienTuMayTinhTien.xlsx
@@ -10708,6 +10708,757 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" s="4" t="n">
+        <v>155.0</v>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>3148</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H161" s="7"/>
+      <c r="I161" s="6"/>
+      <c r="J161" s="6" t="inlineStr">
+        <is>
+          <t>452 trần phú,phường vũng at2u,tp hồ chí minh</t>
+        </is>
+      </c>
+      <c r="K161" s="6"/>
+      <c r="L161" s="13" t="n">
+        <v>6244359.0</v>
+      </c>
+      <c r="M161" s="13" t="n">
+        <v>598641.0</v>
+      </c>
+      <c r="N161" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O161" s="13" t="n">
+        <v>6843000.0</v>
+      </c>
+      <c r="P161" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q161" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="n">
+        <v>156.0</v>
+      </c>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>3149</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H162" s="7"/>
+      <c r="I162" s="6"/>
+      <c r="J162" s="6" t="inlineStr">
+        <is>
+          <t>55-57 ngư phủ</t>
+        </is>
+      </c>
+      <c r="K162" s="6"/>
+      <c r="L162" s="13" t="n">
+        <v>3203788.0</v>
+      </c>
+      <c r="M162" s="13" t="n">
+        <v>317212.0</v>
+      </c>
+      <c r="N162" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O162" s="13" t="n">
+        <v>3521000.0</v>
+      </c>
+      <c r="P162" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q162" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="n">
+        <v>157.0</v>
+      </c>
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H163" s="7"/>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>7 Lê Hồng Phong</t>
+        </is>
+      </c>
+      <c r="J163" s="6" t="inlineStr">
+        <is>
+          <t>7 Lê Hồng Phong , Phường Tam Thắng, Thành Phố Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K163" s="6"/>
+      <c r="L163" s="13" t="n">
+        <v>5032828.0</v>
+      </c>
+      <c r="M163" s="13" t="n">
+        <v>487172.0</v>
+      </c>
+      <c r="N163" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O163" s="13" t="n">
+        <v>5520000.0</v>
+      </c>
+      <c r="P163" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q163" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="n">
+        <v>158.0</v>
+      </c>
+      <c r="B164" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D164" s="7" t="inlineStr">
+        <is>
+          <t>3151</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H164" s="7"/>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ không cung cấp thông tin</t>
+        </is>
+      </c>
+      <c r="J164" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ không cung cấp thông tin</t>
+        </is>
+      </c>
+      <c r="K164" s="6"/>
+      <c r="L164" s="13" t="n">
+        <v>3896364.0</v>
+      </c>
+      <c r="M164" s="13" t="n">
+        <v>389636.0</v>
+      </c>
+      <c r="N164" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O164" s="13" t="n">
+        <v>4286000.0</v>
+      </c>
+      <c r="P164" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q164" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="n">
+        <v>159.0</v>
+      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D165" s="7" t="inlineStr">
+        <is>
+          <t>3152</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G165" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H165" s="7"/>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ không cung cấp thông tin</t>
+        </is>
+      </c>
+      <c r="J165" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ không cung cấp thông tin</t>
+        </is>
+      </c>
+      <c r="K165" s="6"/>
+      <c r="L165" s="13" t="n">
+        <v>6329208.0</v>
+      </c>
+      <c r="M165" s="13" t="n">
+        <v>607792.0</v>
+      </c>
+      <c r="N165" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O165" s="13" t="n">
+        <v>6937000.0</v>
+      </c>
+      <c r="P165" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q165" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="n">
+        <v>160.0</v>
+      </c>
+      <c r="B166" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>3153</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G166" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H166" s="7"/>
+      <c r="I166" s="6"/>
+      <c r="J166" s="6" t="inlineStr">
+        <is>
+          <t>cảng kamad</t>
+        </is>
+      </c>
+      <c r="K166" s="6"/>
+      <c r="L166" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M166" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N166" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O166" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P166" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q166" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="n">
+        <v>161.0</v>
+      </c>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>3154</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H167" s="7"/>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>60A Bạch Đằng</t>
+        </is>
+      </c>
+      <c r="J167" s="6" t="inlineStr">
+        <is>
+          <t>60A Bạch Đằng, Phường Vũng Tàu , Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K167" s="6"/>
+      <c r="L167" s="13" t="n">
+        <v>1.2136363E7</v>
+      </c>
+      <c r="M167" s="13" t="n">
+        <v>1213637.0</v>
+      </c>
+      <c r="N167" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O167" s="13" t="n">
+        <v>1.335E7</v>
+      </c>
+      <c r="P167" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q167" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="n">
+        <v>162.0</v>
+      </c>
+      <c r="B168" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>3155</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G168" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H168" s="7"/>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>60/37 bạch đằng</t>
+        </is>
+      </c>
+      <c r="J168" s="6" t="inlineStr">
+        <is>
+          <t>60/37 bạch đằng, Phường Vũng Tàu Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K168" s="6"/>
+      <c r="L168" s="13" t="n">
+        <v>4826430.0</v>
+      </c>
+      <c r="M168" s="13" t="n">
+        <v>441570.0</v>
+      </c>
+      <c r="N168" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O168" s="13" t="n">
+        <v>5268000.0</v>
+      </c>
+      <c r="P168" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q168" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="n">
+        <v>163.0</v>
+      </c>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>3156</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H169" s="7"/>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>752 trần phú</t>
+        </is>
+      </c>
+      <c r="J169" s="6" t="inlineStr">
+        <is>
+          <t>752 trần phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K169" s="6"/>
+      <c r="L169" s="13" t="n">
+        <v>4290236.0</v>
+      </c>
+      <c r="M169" s="13" t="n">
+        <v>398764.0</v>
+      </c>
+      <c r="N169" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O169" s="13" t="n">
+        <v>4689000.0</v>
+      </c>
+      <c r="P169" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q169" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="n">
+        <v>164.0</v>
+      </c>
+      <c r="B170" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>3157</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G170" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H170" s="7" t="inlineStr">
+        <is>
+          <t>8029936597-001</t>
+        </is>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH COFFEE TIGER</t>
+        </is>
+      </c>
+      <c r="J170" s="6" t="inlineStr">
+        <is>
+          <t>9 đường Trương Vĩnh Ký, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K170" s="6"/>
+      <c r="L170" s="13" t="n">
+        <v>3610033.0</v>
+      </c>
+      <c r="M170" s="13" t="n">
+        <v>329167.0</v>
+      </c>
+      <c r="N170" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O170" s="13" t="n">
+        <v>3939200.0</v>
+      </c>
+      <c r="P170" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q170" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="n">
+        <v>165.0</v>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>C25MTD</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>3158</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H171" s="7"/>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>75/16 Trần Xuân Độ</t>
+        </is>
+      </c>
+      <c r="J171" s="6" t="inlineStr">
+        <is>
+          <t>75/16 Trần Xuân Độ, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K171" s="6"/>
+      <c r="L171" s="13" t="n">
+        <v>9655471.0</v>
+      </c>
+      <c r="M171" s="13" t="n">
+        <v>931529.0</v>
+      </c>
+      <c r="N171" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O171" s="13" t="n">
+        <v>1.0587E7</v>
+      </c>
+      <c r="P171" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q171" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>
